--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_185_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_185_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>20</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1341,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>28</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>-7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>16</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>6</v>
@@ -3827,16 +3827,16 @@
         <v>66</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
         <v>26</v>
@@ -4880,7 +4880,7 @@
         <v>14</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -5468,10 +5468,10 @@
         <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>3</v>
@@ -5860,16 +5860,16 @@
         <v>27</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>3</v>
@@ -6252,7 +6252,7 @@
         <v>24</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>120</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>20</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_185_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_185_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -695,17 +695,17 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P3" t="n">
         <v>12</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>95.24</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3503,10 +3503,10 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
@@ -3886,11 +3886,11 @@
         <v>4</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
         <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5872,10 +5872,10 @@
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y48" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="AA48" t="n">
